--- a/avellana_data.xlsx
+++ b/avellana_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ffuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A11AC90-7D9B-4294-A6BB-B1D51C9D75F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4394050B-DD2D-46AF-9765-521E4A31E875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -610,7 +610,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>29</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -626,7 +626,7 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -642,7 +642,7 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>29</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -658,7 +658,7 @@
         <v>22</v>
       </c>
       <c r="B12">
-        <v>29</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">

--- a/avellana_data.xlsx
+++ b/avellana_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ffuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4394050B-DD2D-46AF-9765-521E4A31E875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A136762-E56E-4F77-897B-2FABA2B8105B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,7 +594,7 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -602,7 +602,7 @@
         <v>15</v>
       </c>
       <c r="B5">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -610,7 +610,7 @@
         <v>16</v>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -618,7 +618,7 @@
         <v>17</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -626,7 +626,7 @@
         <v>18</v>
       </c>
       <c r="B8">
-        <v>90</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -634,7 +634,7 @@
         <v>19</v>
       </c>
       <c r="B9">
-        <v>29</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -642,7 +642,7 @@
         <v>20</v>
       </c>
       <c r="B10">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -650,7 +650,7 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">

--- a/avellana_data.xlsx
+++ b/avellana_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ffuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A136762-E56E-4F77-897B-2FABA2B8105B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0389CA0B-F32D-4C79-8414-BAC6CB668DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VentasMensuales" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Mes</t>
   </si>
@@ -116,13 +116,40 @@
   </si>
   <si>
     <t>Pop-up stores</t>
+  </si>
+  <si>
+    <t>Enero</t>
+  </si>
+  <si>
+    <t>Febrero</t>
+  </si>
+  <si>
+    <t>Marzo</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>Junio</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Septiembre</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +162,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -462,7 +495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -475,29 +508,102 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>124</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>158</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B13">
         <v>205</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/avellana_data.xlsx
+++ b/avellana_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ffuentes\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0389CA0B-F32D-4C79-8414-BAC6CB668DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885A8201-1EA8-4657-BE2B-A0B68B2F2CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -535,7 +535,7 @@
         <v>34</v>
       </c>
       <c r="B5">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -543,7 +543,7 @@
         <v>35</v>
       </c>
       <c r="B6">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -551,7 +551,7 @@
         <v>36</v>
       </c>
       <c r="B7">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -559,7 +559,7 @@
         <v>37</v>
       </c>
       <c r="B8">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -575,7 +575,7 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -583,7 +583,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>124</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -591,7 +591,7 @@
         <v>3</v>
       </c>
       <c r="B12">
-        <v>158</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -599,7 +599,7 @@
         <v>4</v>
       </c>
       <c r="B13">
-        <v>205</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
